--- a/11-bao-gia-khach/NOIBO-Bao-Gia-PR-Thanh-Nien-Trung-Tam-Piano-2026-10-27.xlsx
+++ b/11-bao-gia-khach/NOIBO-Bao-Gia-PR-Thanh-Nien-Trung-Tam-Piano-2026-10-27.xlsx
@@ -600,20 +600,20 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Life Media (Plan PR 27/10)</t>
+          <t>Goodcom (file Combat 2026, tab 27.10)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>15000000</v>
+        <v>12037037</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>12150000</v>
+        <v>10231481</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>13365000</v>
+        <v>11255000</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1215000</v>
+        <v>1023519</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Niêm yết 17,820,000 - CK 25% (số trình bày, không phải giá thật). Giá nguồn 15.000.000, CK nguồn 19% = 12.150.000 (vốn). Bán = vốn x 1,10.</t>
+          <t>Niêm yết 15,010,000 - CK 25% (số trình bày, không phải giá thật). Giá gốc Goodcom 12.037.037 (tiểu mục Giáo dục), CK nguồn 15% = 10.231.481 (vốn). Bán = vốn x 1,10, làm tròn lên nghìn.</t>
         </is>
       </c>
     </row>
@@ -670,12 +670,12 @@
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>(A) Life Media vs DanaSEO cùng vị trí</t>
+          <t>(A) Goodcom vs Life vs DanaSEO</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Life: vốn 12.150.000, bán 13.365.000. DanaSEO: vốn thật 13.950.000, bán 14.725.000. Life rẻ hơn vốn 1.800.000 và giá bán rẻ hơn 1.360.000; lãi bài (A) 1.215.000 (cao hơn lãi DanaSEO 775.000).</t>
+          <t>Goodcom: vốn 10.231.481, bán 11.255.000. Life: vốn 12.150.000, bán 13.365.000. DanaSEO: vốn thật 13.950.000, bán 14.725.000. Goodcom rẻ hơn Life 1.918.519 vốn, rẻ hơn DanaSEO 3.718.519 vốn; lãi bài (A) 1.023.519.</t>
         </is>
       </c>
     </row>
@@ -687,31 +687,31 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Life: 1.000 chữ + 5 ảnh + 2 hyperlink free, tiêu đề 17 chữ, sapo 60 chữ, duyệt 3-5 ngày. DanaSEO: dưới 1.000 từ, dưới 3 ảnh, 2 link nofollow. Life hơn về ảnh.</t>
+          <t>Goodcom: 1.000 từ, 5 ảnh, 2 link (tiểu mục Giáo dục). Life: 1.000 chữ, 5 ảnh, 2 hyperlink, duyệt 3-5 ngày. DanaSEO: dưới 1.000 từ, dưới 3 ảnh, 2 link nofollow. Goodcom và Life cùng quy cách.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Rủi ro Life</t>
+          <t>Rủi ro Goodcom</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Plan ghi: giá check tại thời điểm hiện tại, có thể đổi theo chính sách và nội dung BBT duyệt; có thể phát sinh chi phí khi duyệt. Nên chốt lại với Life trước khi gửi khách; chưa có giá thêm link của Life.</t>
+          <t>File ghi hiệu lực 10 ngày; giá chưa VAT và chưa gồm phí edit; có thể điều chỉnh theo đơn vị chủ quản; tiểu mục "tuỳ nội dung mới duyệt được xem vào mục nào phù hợp". Nếu bài xếp tiểu mục Doanh nghiệp/Kinh tế thì giá gốc 13.888.889, vốn 11.805.556, bán 12.986.000.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Goodcom</t>
+          <t>Life Media</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Chưa có giá Thanh Niên của Goodcom trong kho. Có thì bán = giá Goodcom x 1,10.</t>
+          <t>Giá Life 15.000.000 (Plan PR 27/10) đắt hơn Goodcom, không dùng cho (A).</t>
         </is>
       </c>
     </row>
@@ -985,9 +985,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
